--- a/artfynd/A 52355-2021 artfynd.xlsx
+++ b/artfynd/A 52355-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 52355-2021 artfynd.xlsx
+++ b/artfynd/A 52355-2021 artfynd.xlsx
@@ -675,19 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>83496177</v>
+        <v>83496169</v>
       </c>
       <c r="B2" t="n">
-        <v>100515</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103403</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>397115.9421589596</v>
+        <v>397121</v>
       </c>
       <c r="R2" t="n">
-        <v>6162408.819930202</v>
+        <v>6162414</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,7 +744,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>D85B1B0F-7E40-4424-865C-538DA6E6FD28</t>
+          <t>B925E5AA-EECF-4027-988C-AD8A81FFB26C</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -757,19 +752,9 @@
           <t>2008-12-15</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2008-12-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -803,16 +788,11 @@
         <v>83496170</v>
       </c>
       <c r="B3" t="n">
-        <v>100515</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103403</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -844,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>397122.9067813548</v>
+        <v>397123</v>
       </c>
       <c r="R3" t="n">
-        <v>6162416.00234731</v>
+        <v>6162416</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,19 +862,9 @@
           <t>2008-12-15</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2008-12-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,19 +895,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>83496169</v>
+        <v>83496177</v>
       </c>
       <c r="B4" t="n">
-        <v>100515</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103403</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -969,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>397120.5896705295</v>
+        <v>397116</v>
       </c>
       <c r="R4" t="n">
-        <v>6162413.796468622</v>
+        <v>6162409</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,7 +964,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>B925E5AA-EECF-4027-988C-AD8A81FFB26C</t>
+          <t>D85B1B0F-7E40-4424-865C-538DA6E6FD28</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1007,19 +972,9 @@
           <t>2008-12-15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2008-12-15</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
